--- a/Outputs/PtX_demand_NL.xlsx
+++ b/Outputs/PtX_demand_NL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,55 +488,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004849937118253851</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0007355988565083813</v>
-      </c>
+        <v>0.007780804891708162</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05047885156377294</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0005869991914447611</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>2.747231989446974e-09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0005684959714187</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2030</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>0.01553277004395703</v>
-      </c>
+      <c r="C3" t="n">
+        <v>0.004849937118253851</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0007355988565083813</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2.747231989446974e-09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0005684959714187</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -544,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.04109300256402446</v>
+        <v>0.01553277004395703</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -557,14 +561,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2030</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.04109300256402446</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -576,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -584,24 +590,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.001117919891598643</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0001445082443118065</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>0.0001045785519216255</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -609,14 +609,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.001117919891598643</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.002829808492279384</v>
+        <v>0.0001445082443118065</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.0004257505736205</v>
+        <v>0.0001045785519216255</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -624,7 +626,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -633,17 +635,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.002829808492279384</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.0004257505736205</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -652,29 +658,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.0126833508877942</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.000180631468834</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.007516691846522</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0201073086329636</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0001371059994361</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0259973854341129</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -684,28 +678,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.1353900801138015</v>
+        <v>0.0126833508877942</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0012721344657017</v>
+        <v>0.000180631468834</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06869851052436481</v>
+        <v>0.007516691846522</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1270774641633629</v>
+        <v>0.0201073086329636</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0008299029030332</v>
+        <v>0.0001371059994361</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2440411302673871</v>
+        <v>0.0259973854341129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -714,17 +708,29 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.1353900801138015</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0012721344657017</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.06869851052436481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1270774641633629</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0008299029030332</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2440411302673871</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -732,9 +738,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>8.820543722503238e-05</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -745,102 +749,102 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
       <c r="C13" t="n">
-        <v>0.004849937118253851</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0566257726079815</v>
-      </c>
+        <v>0.04364943406428466</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.001206125328823675</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1517833465946953</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0014527659345357</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.07621520511811879</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1482835978932873</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0009670089024692999</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2700385157015</v>
-      </c>
+        <v>0.01085512795941308</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.01992463443234875</v>
-      </c>
+        <v>2030</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.003584861244587386</v>
-      </c>
+      <c r="E14" t="n">
+        <v>8.820543722503238e-05</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>2.299736609075437e-07</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0008298263079343</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.05628017607424667</v>
+      </c>
       <c r="D15" t="n">
-        <v>0.0168924454810686</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>0.1071046241717544</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01264825247968151</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1517833465946953</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0014527659345357</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.07621520511811879</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1482835978932873</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0009670089024692999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2700385157015</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.007438161820342556</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.04469011666957987</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>0.05192814390487584</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0005152157226032678</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -851,22 +855,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2040</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0.01992463443234875</v>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1.228488936317878e-09</v>
+        <v>0.003584861244587386</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>2.299736609075437e-07</v>
+      </c>
       <c r="I17" t="n">
-        <v>2.590471797961311e-10</v>
+        <v>0.0008298263079343</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -874,55 +882,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2040</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.003849401952734385</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.000199066963544479</v>
-      </c>
+      <c r="D18" t="n">
+        <v>0.0168924454810686</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>0.0001783309686270224</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2040</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.04469011666957987</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.001465163543308868</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0.0004520604269044</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -931,17 +933,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1.228488936317878e-09</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2.590471797961311e-10</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -949,30 +955,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.003849401952734385</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.005149611513421999</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0002944590938452</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.009150498120629199</v>
-      </c>
+        <v>0.000199066963544479</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0133033051550514</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0001665615372356</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0301427250014024</v>
-      </c>
+        <v>0.0001783309686270224</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -982,28 +982,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.0371026525835975</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0013676152776829</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.06476985866080399</v>
-      </c>
+        <v>0.001465163543308868</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0569005095930935</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0007364645791344999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.2342383394986932</v>
-      </c>
+        <v>0.0004520604269044</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1022,7 +1014,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1030,94 +1022,94 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.0003082428755395282</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.005149611513421999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0002944590938452</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.009150498120629199</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0133033051550514</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0001665615372356</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0301427250014024</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2040</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.01992463443234875</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.06158256215064847</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.004157644828273913</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.04750135707694917</v>
+        <v>0.0371026525835975</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0016620743715281</v>
+        <v>0.0013676152776829</v>
       </c>
       <c r="H25" t="n">
-        <v>0.07392058675509409</v>
+        <v>0.06476985866080399</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0716640327106578</v>
+        <v>0.0569005095930935</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0009030261163700999</v>
+        <v>0.0007364645791344999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2643810645000956</v>
+        <v>0.2342383394986932</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.05183475366938666</v>
-      </c>
+        <v>2040</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.004948462754339134</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>3.897868312291493e-07</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0013235829872827</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.02988695164852312</v>
+      </c>
       <c r="D27" t="n">
-        <v>0.0189887875350703</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>3.274180926382542e-18</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.006236467242410869</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1128,17 +1120,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.05023613255447214</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.0003082428755395282</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1149,70 +1141,88 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.05724974790121443</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1135107060555243</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.01090932779328805</v>
+      </c>
       <c r="F29" t="n">
-        <v>4.26388055600474e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.04750135707694917</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0016620743715281</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07392058675509409</v>
+      </c>
       <c r="I29" t="n">
-        <v>6.648712955993891e-09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.0716640327106578</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0009030261163700999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2643810645000956</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.006909876127734959</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.05416265693664087</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.00730587944779736</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.440111278495978e-05</v>
-      </c>
+        <v>0.0004045402625580216</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>5.110695766263079e-05</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0.05183475366938666</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>5.254108439513384e-05</v>
+        <v>0.004948462754339134</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>3.897868312291493e-07</v>
+      </c>
       <c r="I31" t="n">
-        <v>0.0001681023845866508</v>
+        <v>0.0013235829872827</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1220,69 +1230,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2050</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0.0189887875350703</v>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>8.125075711298653e-11</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.084333688676964e-11</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.525438284182439e-10</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.205038687847974e-10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.140750937685103e-12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.589051001723168e-09</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2050</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.05023613255447214</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0007273686614734217</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0005261467020982</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0119851810380149</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0034314317226407</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0002142245127542</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0425923219994788</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1292,28 +1282,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0047371849411114</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0012335310614793</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0587379235030874</v>
-      </c>
+        <v>4.26388055600474e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.010132367438695</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.000633912547509</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.2155548826456272</v>
-      </c>
+        <v>6.648712955993891e-09</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1321,18 +1303,24 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0.00730587944779736</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.440111278495978e-05</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>5.110695766263079e-05</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1340,50 +1328,204 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.0006387356599515332</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>5.254108439513384e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0.0001681023845866508</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2050</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.05183475366938666</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.06922492008954244</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.007944615107748893</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>8.125075711298653e-11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.084333688676964e-11</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.525438284182439e-10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.205038687847974e-10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.140750937685103e-12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.589051001723168e-09</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0007273686614734217</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0005261467020982</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0119851810380149</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0034314317226407</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0002142245127542</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0425923219994788</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0047371849411114</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0012335310614793</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0587379235030874</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.010132367438695</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.000633912547509</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2155548826456272</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.0006387356599515332</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.05874462979712162</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1233875770261833</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.008349155370306914</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.01048996289923536</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.001759677774420837</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.07072349468047735</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.01510659836008451</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.0008481370614039508</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.258147207234157</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_NL.xlsx
+++ b/Outputs/PtX_demand_NL.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.0005869991914447611</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.01690386163585621</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0073142933863905</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.008863992224353801</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0012424747403241</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -730,15 +738,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2030</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0.04364943406428466</v>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0.01085512795941308</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -749,19 +761,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.04364943406428466</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>0.01085512795941308</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -809,19 +817,19 @@
         <v>0.01264825247968151</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1517833465946953</v>
+        <v>0.1686872082305515</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0014527659345357</v>
+        <v>0.008767059320926199</v>
       </c>
       <c r="H15" t="n">
         <v>0.07621520511811879</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1482835978932873</v>
+        <v>0.1571475901176411</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0009670089024692999</v>
+        <v>0.0022094836427934</v>
       </c>
       <c r="K15" t="n">
         <v>0.2700385157015</v>
@@ -845,11 +853,19 @@
       <c r="E16" t="n">
         <v>0.0005152157226032678</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.047665593825103</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.008583997934423999</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0305448962805851</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0012253688294541</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1076,15 +1092,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2040</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0.02988695164852312</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.274180926382542e-18</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.006236467242410869</v>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1095,21 +1117,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2040</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.02988695164852312</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.274180926382542e-18</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.006236467242410869</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1157,19 +1173,19 @@
         <v>0.01090932779328805</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04750135707694917</v>
+        <v>0.09516695090205217</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0016620743715281</v>
+        <v>0.0102460723059521</v>
       </c>
       <c r="H29" t="n">
         <v>0.07392058675509409</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0716640327106578</v>
+        <v>0.1022089289912429</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0009030261163700999</v>
+        <v>0.0021283949458242</v>
       </c>
       <c r="K29" t="n">
         <v>0.2643810645000956</v>
@@ -1193,11 +1209,19 @@
       <c r="E30" t="n">
         <v>0.0004045402625580216</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.0551511539971559</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0096397795111195</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0454022673414259</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0012514986687594</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1436,7 +1460,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1455,7 +1479,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1508,22 +1532,22 @@
         <v>0.1233875770261833</v>
       </c>
       <c r="E43" t="n">
-        <v>0.008349155370306914</v>
+        <v>0.008349155370306916</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01048996289923536</v>
+        <v>0.06564111689639127</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001759677774420837</v>
+        <v>0.01139945728554034</v>
       </c>
       <c r="H43" t="n">
         <v>0.07072349468047735</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01510659836008451</v>
+        <v>0.0605088657015104</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0008481370614039508</v>
+        <v>0.002099635730163351</v>
       </c>
       <c r="K43" t="n">
         <v>0.258147207234157</v>
